--- a/UTCUTS/_GDP_Ref.xlsx
+++ b/UTCUTS/_GDP_Ref.xlsx
@@ -1605,7 +1605,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9F36BBF-7F54-4A22-A925-3310D1D10228}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F41C7-30D6-4060-A91A-237533820EF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
